--- a/apps/web/public/templates/bank-template.xlsx
+++ b/apps/web/public/templates/bank-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -19,9 +19,15 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
     <t>Check Number</t>
   </si>
   <si>
+    <t>Reference</t>
+  </si>
+  <si>
     <t>Debit</t>
   </si>
   <si>
@@ -37,22 +43,58 @@
     <t>ACME OFFICE SUPPLY</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>125.50</t>
+  </si>
+  <si>
+    <t>9874.50</t>
+  </si>
+  <si>
     <t>2026-08-03</t>
   </si>
   <si>
     <t>PAYROLL ACH</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3200.00</t>
+  </si>
+  <si>
+    <t>6674.50</t>
+  </si>
+  <si>
     <t>2026-08-05</t>
   </si>
   <si>
     <t>CLIENT PAYMENT NORTH</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>2026-08-08</t>
   </si>
   <si>
     <t>CHECK 1052 RENT</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>1600.00</t>
+  </si>
+  <si>
+    <t>8274.50</t>
   </si>
 </sst>
 </file>
@@ -429,10 +471,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -451,64 +493,115 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>125.5</v>
-      </c>
-      <c r="F2">
-        <v>9874.5</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>3200</v>
-      </c>
-      <c r="F3">
-        <v>6674.5</v>
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4">
-        <v>3200</v>
-      </c>
-      <c r="F4">
-        <v>9874.5</v>
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>1052</v>
-      </c>
-      <c r="D5">
-        <v>1600</v>
-      </c>
-      <c r="F5">
-        <v>8274.5</v>
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
